--- a/artfynd/A 19094-2025 artfynd.xlsx
+++ b/artfynd/A 19094-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124324443</v>
+        <v>124324447</v>
       </c>
       <c r="B2" t="n">
         <v>96985</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571107</v>
+        <v>571302</v>
       </c>
       <c r="R2" t="n">
-        <v>6687490</v>
+        <v>6687215</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124324447</v>
+        <v>124324443</v>
       </c>
       <c r="B3" t="n">
         <v>96985</v>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571302</v>
+        <v>571107</v>
       </c>
       <c r="R3" t="n">
-        <v>6687215</v>
+        <v>6687490</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 19094-2025 artfynd.xlsx
+++ b/artfynd/A 19094-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124324447</v>
+        <v>124324443</v>
       </c>
       <c r="B2" t="n">
         <v>96985</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571302</v>
+        <v>571107</v>
       </c>
       <c r="R2" t="n">
-        <v>6687215</v>
+        <v>6687490</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124324443</v>
+        <v>124324447</v>
       </c>
       <c r="B3" t="n">
         <v>96985</v>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571107</v>
+        <v>571302</v>
       </c>
       <c r="R3" t="n">
-        <v>6687490</v>
+        <v>6687215</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 19094-2025 artfynd.xlsx
+++ b/artfynd/A 19094-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124324447</v>
+        <v>124324443</v>
       </c>
       <c r="B2" t="n">
         <v>96985</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571302</v>
+        <v>571107</v>
       </c>
       <c r="R2" t="n">
-        <v>6687215</v>
+        <v>6687490</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124324443</v>
+        <v>124324444</v>
       </c>
       <c r="B3" t="n">
         <v>96985</v>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571107</v>
+        <v>571268</v>
       </c>
       <c r="R3" t="n">
-        <v>6687490</v>
+        <v>6687488</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124324444</v>
+        <v>124324447</v>
       </c>
       <c r="B4" t="n">
         <v>96985</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571268</v>
+        <v>571302</v>
       </c>
       <c r="R4" t="n">
-        <v>6687488</v>
+        <v>6687215</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 19094-2025 artfynd.xlsx
+++ b/artfynd/A 19094-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124324443</v>
+        <v>124324444</v>
       </c>
       <c r="B2" t="n">
         <v>96985</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571107</v>
+        <v>571268</v>
       </c>
       <c r="R2" t="n">
-        <v>6687490</v>
+        <v>6687488</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124324444</v>
+        <v>124324447</v>
       </c>
       <c r="B3" t="n">
         <v>96985</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571268</v>
+        <v>571302</v>
       </c>
       <c r="R3" t="n">
-        <v>6687488</v>
+        <v>6687215</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124324447</v>
+        <v>124324443</v>
       </c>
       <c r="B4" t="n">
         <v>96985</v>
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571302</v>
+        <v>571107</v>
       </c>
       <c r="R4" t="n">
-        <v>6687215</v>
+        <v>6687490</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 19094-2025 artfynd.xlsx
+++ b/artfynd/A 19094-2025 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124324447</v>
+        <v>124324443</v>
       </c>
       <c r="B3" t="n">
         <v>96985</v>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571302</v>
+        <v>571107</v>
       </c>
       <c r="R3" t="n">
-        <v>6687215</v>
+        <v>6687490</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124324443</v>
+        <v>124324447</v>
       </c>
       <c r="B4" t="n">
         <v>96985</v>
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571107</v>
+        <v>571302</v>
       </c>
       <c r="R4" t="n">
-        <v>6687490</v>
+        <v>6687215</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 19094-2025 artfynd.xlsx
+++ b/artfynd/A 19094-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124324444</v>
+        <v>124324443</v>
       </c>
       <c r="B2" t="n">
         <v>96985</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571268</v>
+        <v>571107</v>
       </c>
       <c r="R2" t="n">
-        <v>6687488</v>
+        <v>6687490</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124324443</v>
+        <v>124324447</v>
       </c>
       <c r="B3" t="n">
         <v>96985</v>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571107</v>
+        <v>571302</v>
       </c>
       <c r="R3" t="n">
-        <v>6687490</v>
+        <v>6687215</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124324447</v>
+        <v>124324444</v>
       </c>
       <c r="B4" t="n">
         <v>96985</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571302</v>
+        <v>571268</v>
       </c>
       <c r="R4" t="n">
-        <v>6687215</v>
+        <v>6687488</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 19094-2025 artfynd.xlsx
+++ b/artfynd/A 19094-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124324447</v>
+        <v>124324444</v>
       </c>
       <c r="B2" t="n">
         <v>96985</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571302</v>
+        <v>571268</v>
       </c>
       <c r="R2" t="n">
-        <v>6687215</v>
+        <v>6687488</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124324444</v>
+        <v>124324447</v>
       </c>
       <c r="B4" t="n">
         <v>96985</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571268</v>
+        <v>571302</v>
       </c>
       <c r="R4" t="n">
-        <v>6687488</v>
+        <v>6687215</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 19094-2025 artfynd.xlsx
+++ b/artfynd/A 19094-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124324444</v>
+        <v>124324447</v>
       </c>
       <c r="B2" t="n">
         <v>96985</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571268</v>
+        <v>571302</v>
       </c>
       <c r="R2" t="n">
-        <v>6687488</v>
+        <v>6687215</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124324447</v>
+        <v>124324444</v>
       </c>
       <c r="B4" t="n">
         <v>96985</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571302</v>
+        <v>571268</v>
       </c>
       <c r="R4" t="n">
-        <v>6687215</v>
+        <v>6687488</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 19094-2025 artfynd.xlsx
+++ b/artfynd/A 19094-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124324447</v>
+        <v>124324444</v>
       </c>
       <c r="B2" t="n">
         <v>96985</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571302</v>
+        <v>571268</v>
       </c>
       <c r="R2" t="n">
-        <v>6687215</v>
+        <v>6687488</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124324443</v>
+        <v>124324447</v>
       </c>
       <c r="B3" t="n">
         <v>96985</v>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571107</v>
+        <v>571302</v>
       </c>
       <c r="R3" t="n">
-        <v>6687490</v>
+        <v>6687215</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124324444</v>
+        <v>124324443</v>
       </c>
       <c r="B4" t="n">
         <v>96985</v>
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571268</v>
+        <v>571107</v>
       </c>
       <c r="R4" t="n">
-        <v>6687488</v>
+        <v>6687490</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 19094-2025 artfynd.xlsx
+++ b/artfynd/A 19094-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124324444</v>
+        <v>124324443</v>
       </c>
       <c r="B2" t="n">
-        <v>96985</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571268</v>
+        <v>571107</v>
       </c>
       <c r="R2" t="n">
-        <v>6687488</v>
+        <v>6687490</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124324447</v>
+        <v>124324444</v>
       </c>
       <c r="B3" t="n">
-        <v>96985</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571302</v>
+        <v>571268</v>
       </c>
       <c r="R3" t="n">
-        <v>6687215</v>
+        <v>6687488</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124324443</v>
+        <v>124324447</v>
       </c>
       <c r="B4" t="n">
-        <v>96985</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,13 +926,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571107</v>
+        <v>571302</v>
       </c>
       <c r="R4" t="n">
-        <v>6687490</v>
+        <v>6687215</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 19094-2025 artfynd.xlsx
+++ b/artfynd/A 19094-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124324443</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124324444</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,8 +1005,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124324447</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>